--- a/etf_holdings/2026-08-31_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-08-31_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL19"/>
+  <dimension ref="A1:BB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,66 +687,16 @@
           <t>00992A_股數變化</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>00405A_異動類型</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>00405A_調整方向</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>00405A_股票名稱_昨日</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>00405A_股票名稱_今日</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>00405A_權重_昨日</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>00405A_權重_今日</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>00405A_權重變化</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>00405A_股數_昨日</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>00405A_股數_今日</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>00405A_股數變化</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -754,7 +704,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00405A,00981A,00982A,00985A</t>
+          <t>00981A,00982A,00985A,00992A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -769,38 +719,38 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.21%</t>
+          <t>3.86%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5979000</v>
+        <v>19479000</v>
       </c>
       <c r="M2" t="n">
-        <v>5949000</v>
+        <v>18679000</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-30,000</t>
+          <t>-800,000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -815,38 +765,38 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>378000</v>
+        <v>956000</v>
       </c>
       <c r="W2" t="n">
-        <v>376000</v>
+        <v>950000</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -871,206 +821,142 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>日月光投資控股</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>奇鋐科技</t>
+          <t>日月光投資控股</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>68000</v>
+        <v>335000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>76000</v>
+        <v>435000</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>8,000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>1.01%</t>
+        </is>
+      </c>
       <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>716000</v>
+      </c>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>9.20%</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>7.90%</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>-1.30%</t>
-        </is>
-      </c>
-      <c r="BJ2" t="n">
-        <v>803000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>658000</v>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>-145,000</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00981A,00982A,00985A,00992A</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+          <t>00982A,00985A,00992A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4.12%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>3.86%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-0.26%</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>19479000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>18679000</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>-800,000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>5.13%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>5.12%</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>956000</v>
+        <v>185000</v>
       </c>
       <c r="W3" t="n">
-        <v>950000</v>
+        <v>184000</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -1090,93 +976,101 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>日月光投資控股</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>日月光投資控股</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>335000</v>
+        <v>11000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>435000</v>
+        <v>7000</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>-4,000</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr"/>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1.01%</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
+          <t>8.42%</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>7.79%</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>-0.63%</t>
+        </is>
+      </c>
       <c r="AZ3" t="n">
-        <v>716000</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
+        <v>260000</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>235000</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-25,000</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1184,121 +1078,121 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00982A,00985A,00992A</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+          <t>00403A,00981A,00992A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>5.13%</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>5.12%</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>185000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>184000</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-1,000</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9.29%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9.38%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>11264000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11014000</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-250,000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>川湖科技</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>川湖科技</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>1.50%</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>0.95%</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>-0.55%</t>
-        </is>
-      </c>
-      <c r="AP4" t="n">
-        <v>11000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7000</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-4,000</t>
-        </is>
-      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>16.02%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>16.22%</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>+0.20%</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -1311,60 +1205,50 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8.42%</t>
+          <t>7.16%</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>7.79%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>260000</v>
+        <v>1306000</v>
       </c>
       <c r="BA4" t="n">
-        <v>235000</v>
+        <v>1116000</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-25,000</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
+          <t>-190,000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1372,7 +1256,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00403A,00981A,00992A</t>
+          <t>00981A,00982A,00985A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1387,172 +1271,162 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9.29%</t>
+          <t>8.99%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.38%</t>
+          <t>9.24%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>11264000</v>
+        <v>4807000</v>
       </c>
       <c r="M5" t="n">
-        <v>11014000</v>
+        <v>4757000</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-250,000</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+          <t>-50,000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>16.02%</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>16.22%</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>+0.20%</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>11100000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-100,000</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>7.16%</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>6.27%</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>-0.89%</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1306000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1116000</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-190,000</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3.41%</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>319000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>317000</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>台光電子材料</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>台光電子材料</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2.45%</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>+0.78%</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>32000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>47000</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1560,7 +1434,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00981A,00982A,00985A</t>
+          <t>00981A,00985A,00992A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1575,86 +1449,50 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8.99%</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.24%</t>
+          <t>7.07%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4807000</v>
+        <v>5148000</v>
       </c>
       <c r="M6" t="n">
-        <v>4757000</v>
+        <v>5088000</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-50,000</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>3.40%</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>3.41%</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>319000</v>
-      </c>
-      <c r="W6" t="n">
-        <v>317000</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-2,000</t>
-        </is>
-      </c>
+          <t>-60,000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1677,70 +1515,96 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>台光電子材料</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>32000</v>
+        <v>50000</v>
       </c>
       <c r="AQ6" t="n">
-        <v>47000</v>
+        <v>67000</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>15,000</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
+          <t>17,000</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>2.40%</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>-1.07%</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>266000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>145000</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-121,000</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1748,75 +1612,111 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00981A,00985A,00992A</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+          <t>00403A,00982A,00985A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>6.99%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>7.07%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>+0.08%</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>5148000</v>
-      </c>
-      <c r="M7" t="n">
-        <v>5088000</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-60,000</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3.51%</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3.83%</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>+0.32%</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>256000</v>
+      </c>
+      <c r="W7" t="n">
+        <v>255000</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3.20%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>3.80%</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>+0.60%</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>760000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>810000</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
       <c r="AI7" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -1824,111 +1724,65 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>聯發科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>聯發科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>50000</v>
+        <v>24000</v>
       </c>
       <c r="AQ7" t="n">
-        <v>67000</v>
+        <v>16000</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>17,000</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>2.40%</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>1.33%</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>-1.07%</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>266000</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>145000</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-121,000</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1936,19 +1790,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00403A,00982A,00985A</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>00981A,00982A,00985A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6.85%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>7.21%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>5979000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5949000</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-30,000</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -1961,130 +1851,94 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>2.46%</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>256000</v>
+        <v>378000</v>
       </c>
       <c r="W8" t="n">
-        <v>255000</v>
+        <v>376000</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-1,000</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3.20%</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>3.80%</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>+0.60%</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>760000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>810000</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>50,000</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>奇鋐科技</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>24000</v>
+        <v>68000</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16000</v>
+        <v>76000</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-8,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
@@ -2097,26 +1951,16 @@
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2124,7 +1968,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00403A,00405A,00981A</t>
+          <t>00981A,00985A,00992A</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2139,38 +1983,38 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.08%</t>
+          <t>4.13%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2407000</v>
+        <v>9624000</v>
       </c>
       <c r="M9" t="n">
-        <v>2397000</v>
+        <v>9474000</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-10,000</t>
+          <t>-150,000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -2183,136 +2027,126 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>3.75%</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>4.10%</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>+0.35%</t>
-        </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>1087000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1115000</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>28,000</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>8.42%</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>7.76%</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>-0.66%</t>
-        </is>
-      </c>
-      <c r="BJ9" t="n">
-        <v>427000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>370000</v>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>-57,000</t>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>南亞電路板</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>南亞電路板</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.59%</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>1.47%</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>+0.88%</t>
+        </is>
+      </c>
+      <c r="AP9" t="n">
+        <v>48000</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>125000</v>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>77,000</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>+1.00%</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>300000</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>639000</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>339,000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00981A,00985A,00992A</t>
+          <t>00981A,00982A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2327,50 +2161,86 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>3.97%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>4.07%</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.13%</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>9624000</v>
+        <v>89518000</v>
       </c>
       <c r="M10" t="n">
-        <v>9474000</v>
+        <v>89118000</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-150,000</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+          <t>-400,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>5270000</v>
+      </c>
+      <c r="W10" t="n">
+        <v>5243000</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>-27,000</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
@@ -2381,118 +2251,36 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>南亞電路板</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>南亞電路板</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>0.59%</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>1.47%</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>+0.88%</t>
-        </is>
-      </c>
-      <c r="AP10" t="n">
-        <v>48000</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>125000</v>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>77,000</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0.84%</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1.84%</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>+1.00%</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>300000</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>639000</v>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>339,000</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2500,7 +2288,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00981A,00982A</t>
+          <t>00981A,00985A</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2515,86 +2303,50 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>4.52%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>4.72%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>89518000</v>
+        <v>7250000</v>
       </c>
       <c r="M11" t="n">
-        <v>89118000</v>
+        <v>7240000</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-400,000</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>1.33%</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.33%</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>5270000</v>
-      </c>
-      <c r="W11" t="n">
-        <v>5243000</v>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>-27,000</t>
-        </is>
-      </c>
+          <t>-10,000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
@@ -2605,16 +2357,52 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>台達電子工業</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>台達電子工業</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>+0.44%</t>
+        </is>
+      </c>
+      <c r="AP11" t="n">
+        <v>82000</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>105000</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>23,000</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AU11" t="inlineStr"/>
@@ -2625,26 +2413,16 @@
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2667,38 +2445,38 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.52%</t>
+          <t>4.75%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.72%</t>
+          <t>4.66%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>7250000</v>
+        <v>6564000</v>
       </c>
       <c r="M12" t="n">
-        <v>7240000</v>
+        <v>6464000</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-10,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -2733,38 +2511,38 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>台達電子工業</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>台達電子工業</t>
+          <t>智邦科技</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>82000</v>
+        <v>124000</v>
       </c>
       <c r="AQ12" t="n">
-        <v>105000</v>
+        <v>138000</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
@@ -2777,26 +2555,16 @@
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2804,65 +2572,65 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00981A,00985A</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+          <t>00982A,00985A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4.75%</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>4.66%</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>-0.09%</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>6564000</v>
-      </c>
-      <c r="M13" t="n">
-        <v>6464000</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-100,000</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>1796000</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1786000</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>-10,000</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
@@ -2880,43 +2648,43 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>智邦科技</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>4.75%</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="AP13" t="n">
-        <v>124000</v>
+        <v>1448000</v>
       </c>
       <c r="AQ13" t="n">
-        <v>138000</v>
+        <v>1215000</v>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>-233,000</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
@@ -2929,26 +2697,16 @@
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="inlineStr"/>
-      <c r="BJ13" t="inlineStr"/>
-      <c r="BK13" t="inlineStr"/>
-      <c r="BL13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2956,121 +2714,103 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>00982A,00985A</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>技嘉</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>技嘉</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>1.22%</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1.26%</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>1796000</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1786000</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>-10,000</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1.17%</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1.17%</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>12668450</v>
+      </c>
+      <c r="M14" t="n">
+        <v>12818450</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>150,000</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
+      <c r="AG14" t="n">
+        <v>500000</v>
+      </c>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>技嘉科技</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>技嘉科技</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>4.75%</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>4.03%</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>-0.72%</t>
-        </is>
-      </c>
-      <c r="AP14" t="n">
-        <v>1448000</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1215000</v>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-233,000</t>
-        </is>
-      </c>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="inlineStr"/>
@@ -3081,26 +2821,16 @@
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="inlineStr"/>
-      <c r="BJ14" t="inlineStr"/>
-      <c r="BK14" t="inlineStr"/>
-      <c r="BL14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3108,93 +2838,111 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>00403A,00981A</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+          <t>00403A,00982A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1569000</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1562000</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1.17%</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>1.17%</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>12668450</v>
-      </c>
-      <c r="M15" t="n">
-        <v>12818450</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>150,000</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr"/>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>0.08%</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
+        <v>200000</v>
+      </c>
       <c r="AG15" t="n">
-        <v>500000</v>
-      </c>
-      <c r="AH15" t="inlineStr"/>
+        <v>386000</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>186,000</t>
+        </is>
+      </c>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
@@ -3215,26 +2963,16 @@
       <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
-      <c r="BI15" t="inlineStr"/>
-      <c r="BJ15" t="inlineStr"/>
-      <c r="BK15" t="inlineStr"/>
-      <c r="BL15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3242,65 +2980,65 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>00403A,00982A</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>1.32%</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1.46%</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>+0.14%</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>1569000</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1562000</v>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>-7,000</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4.75%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5.08%</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>+0.33%</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>2407000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2397000</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-10,000</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -3313,38 +3051,38 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>4.10%</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>200000</v>
+        <v>1087000</v>
       </c>
       <c r="AG16" t="n">
-        <v>386000</v>
+        <v>1115000</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>186,000</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr"/>
@@ -3367,16 +3105,6 @@
       <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
-      <c r="BI16" t="inlineStr"/>
-      <c r="BJ16" t="inlineStr"/>
-      <c r="BK16" t="inlineStr"/>
-      <c r="BL16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3519,16 +3247,6 @@
       <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="inlineStr"/>
       <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
-      <c r="BI17" t="inlineStr"/>
-      <c r="BJ17" t="inlineStr"/>
-      <c r="BK17" t="inlineStr"/>
-      <c r="BL17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3671,16 +3389,6 @@
       <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="inlineStr"/>
       <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
-      <c r="BI18" t="inlineStr"/>
-      <c r="BJ18" t="inlineStr"/>
-      <c r="BK18" t="inlineStr"/>
-      <c r="BL18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3823,16 +3531,6 @@
       <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="inlineStr"/>
       <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
-      <c r="BI19" t="inlineStr"/>
-      <c r="BJ19" t="inlineStr"/>
-      <c r="BK19" t="inlineStr"/>
-      <c r="BL19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
